--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.2868,0.5317,0.0192,0.4763</t>
-  </si>
-  <si>
-    <t>0.0414,0.0033,0.0089,0.9722</t>
-  </si>
-  <si>
-    <t>0.4419,0.0029,0.0012,0.7542</t>
-  </si>
-  <si>
-    <t>0.2259,0.0009,0.0144,0.8469</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0016,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9804,0.0091,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9909,0.0021,0.0023,0.0010</t>
-  </si>
-  <si>
-    <t>0.9897,0.0040,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.9938,0.0030,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0045,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9957,0.0004,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.8507,0.0147,0.1411,0.0033</t>
-  </si>
-  <si>
-    <t>0.1376,0.0190,0.8851,0.0070</t>
-  </si>
-  <si>
-    <t>0.2693,0.0044,0.8808,0.0005</t>
-  </si>
-  <si>
-    <t>0.2996,0.0112,0.7773,0.0085</t>
-  </si>
-  <si>
-    <t>0.6445,0.1104,0.3538,0.0214</t>
-  </si>
-  <si>
-    <t>0.0085,0.9790,0.0319,0.0002</t>
-  </si>
-  <si>
-    <t>0.0159,0.9740,0.0082,0.0017</t>
-  </si>
-  <si>
-    <t>0.2066,0.8131,0.0136,0.0038</t>
-  </si>
-  <si>
-    <t>0.0686,0.9066,0.0329,0.0021</t>
-  </si>
-  <si>
-    <t>0.0049,0.9906,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.4983,0.0153,0.5983,0.0062</t>
-  </si>
-  <si>
-    <t>0.3510,0.0024,0.7553,0.0112</t>
-  </si>
-  <si>
-    <t>0.0090,0.0047,0.9846,0.0037</t>
-  </si>
-  <si>
-    <t>0.0312,0.0639,0.9291,0.0194</t>
-  </si>
-  <si>
-    <t>0.0644,0.0063,0.9468,0.0040</t>
-  </si>
-  <si>
-    <t>0.1022,0.0078,0.9175,0.0082</t>
-  </si>
-  <si>
-    <t>0.0025,0.0116,0.9650,0.0563</t>
-  </si>
-  <si>
-    <t>0.8753,0.1342,0.0159,0.0016</t>
-  </si>
-  <si>
-    <t>0.5611,0.2947,0.0443,0.0532</t>
-  </si>
-  <si>
-    <t>0.0018,0.0115,0.9814,0.0262</t>
-  </si>
-  <si>
-    <t>0.0239,0.9416,0.0564,0.0009</t>
-  </si>
-  <si>
-    <t>0.7757,0.1294,0.1007,0.0098</t>
-  </si>
-  <si>
-    <t>0.2843,0.2121,0.5935,0.0498</t>
-  </si>
-  <si>
-    <t>0.8465,0.1755,0.0153,0.0016</t>
-  </si>
-  <si>
-    <t>0.0318,0.9249,0.2187,0.0030</t>
-  </si>
-  <si>
-    <t>0.0209,0.5289,0.6427,0.0325</t>
-  </si>
-  <si>
-    <t>0.0029,0.0060,0.9209,0.1385</t>
-  </si>
-  <si>
-    <t>0.0302,0.2284,0.8986,0.0129</t>
-  </si>
-  <si>
-    <t>0.2833,0.0279,0.5852,0.1241</t>
-  </si>
-  <si>
-    <t>0.0363,0.1742,0.9444,0.0041</t>
-  </si>
-  <si>
-    <t>0.0066,0.9778,0.0281,0.0006</t>
-  </si>
-  <si>
-    <t>0.0248,0.0378,0.9491,0.0127</t>
-  </si>
-  <si>
-    <t>0.0192,0.7060,0.0175,0.9336</t>
-  </si>
-  <si>
-    <t>0.0021,0.9514,0.0078,0.3226</t>
-  </si>
-  <si>
-    <t>0.0027,0.9830,0.0254,0.0049</t>
-  </si>
-  <si>
-    <t>0.0039,0.9792,0.0588,0.0041</t>
-  </si>
-  <si>
-    <t>0.0049,0.5433,0.8401,0.0056</t>
-  </si>
-  <si>
-    <t>0.0051,0.2179,0.9855,0.0007</t>
-  </si>
-  <si>
-    <t>0.1538,0.0246,0.8384,0.0226</t>
-  </si>
-  <si>
-    <t>0.0099,0.0030,0.9849,0.0052</t>
-  </si>
-  <si>
-    <t>0.0015,0.0102,0.9941,0.0038</t>
-  </si>
-  <si>
-    <t>0.0765,0.0869,0.8483,0.0048</t>
-  </si>
-  <si>
-    <t>0.9660,0.0221,0.0112,0.0017</t>
-  </si>
-  <si>
-    <t>0.9724,0.0109,0.0053,0.0033</t>
-  </si>
-  <si>
-    <t>0.9609,0.0204,0.0113,0.0040</t>
-  </si>
-  <si>
-    <t>0.0205,0.0800,0.9727,0.0047</t>
-  </si>
-  <si>
-    <t>0.9711,0.0207,0.0071,0.0013</t>
-  </si>
-  <si>
-    <t>0.9822,0.0080,0.0018,0.0025</t>
-  </si>
-  <si>
-    <t>0.9634,0.0314,0.0054,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.9509,0.9569,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.4365,0.8699,0.0007</t>
-  </si>
-  <si>
-    <t>0.0036,0.0116,0.9838,0.0060</t>
-  </si>
-  <si>
-    <t>0.0054,0.8858,0.7755,0.0012</t>
-  </si>
-  <si>
-    <t>0.0046,0.0059,0.9882,0.0054</t>
-  </si>
-  <si>
-    <t>0.0380,0.9462,0.0141,0.0001</t>
-  </si>
-  <si>
-    <t>0.0208,0.9818,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.6897,0.0669,0.3246,0.0282</t>
-  </si>
-  <si>
-    <t>0.7408,0.1083,0.1377,0.0034</t>
-  </si>
-  <si>
-    <t>0.1563,0.0901,0.7293,0.0031</t>
-  </si>
-  <si>
-    <t>0.0009,0.9627,0.6631,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.7528,0.8408,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.9864,0.1792,0.0005</t>
-  </si>
-  <si>
-    <t>0.0041,0.9415,0.4026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0348,0.0162,0.0220,0.9676</t>
-  </si>
-  <si>
-    <t>0.0019,0.0106,0.0002,0.9987</t>
-  </si>
-  <si>
-    <t>0.0036,0.0003,0.0005,0.9974</t>
-  </si>
-  <si>
-    <t>0.0558,0.0079,0.0354,0.9387</t>
-  </si>
-  <si>
-    <t>0.0268,0.0028,0.0106,0.9788</t>
-  </si>
-  <si>
-    <t>0.0025,0.0065,0.0025,0.9965</t>
-  </si>
-  <si>
-    <t>0.0037,0.8990,0.7857,0.0008</t>
-  </si>
-  <si>
-    <t>0.0114,0.6041,0.8964,0.0014</t>
-  </si>
-  <si>
-    <t>0.0364,0.4725,0.7673,0.0048</t>
-  </si>
-  <si>
-    <t>0.0129,0.1397,0.9627,0.0029</t>
-  </si>
-  <si>
-    <t>0.0041,0.9427,0.6242,0.0008</t>
-  </si>
-  <si>
-    <t>0.0136,0.8131,0.6825,0.0049</t>
-  </si>
-  <si>
-    <t>0.9841,0.0061,0.0020,0.0017</t>
-  </si>
-  <si>
-    <t>0.9861,0.0079,0.0014,0.0008</t>
-  </si>
-  <si>
-    <t>0.9681,0.0155,0.0070,0.0034</t>
-  </si>
-  <si>
-    <t>0.9718,0.0244,0.0036,0.0013</t>
-  </si>
-  <si>
-    <t>0.9805,0.0122,0.0011,0.0022</t>
-  </si>
-  <si>
-    <t>0.9941,0.0025,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9736,0.0246,0.0032,0.0012</t>
-  </si>
-  <si>
-    <t>0.9677,0.0336,0.0019,0.0019</t>
-  </si>
-  <si>
-    <t>0.9939,0.0009,0.0005,0.0016</t>
-  </si>
-  <si>
-    <t>0.9924,0.0030,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9972,0.0002,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9967,0.0004,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9738,0.0105,0.0022,0.0046</t>
-  </si>
-  <si>
-    <t>0.9752,0.0197,0.0032,0.0016</t>
-  </si>
-  <si>
-    <t>0.9849,0.0099,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9943,0.0013,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.0218,0.0086,0.9717,0.0045</t>
-  </si>
-  <si>
-    <t>0.0225,0.0269,0.9656,0.0052</t>
-  </si>
-  <si>
-    <t>0.3727,0.0211,0.6568,0.0208</t>
-  </si>
-  <si>
-    <t>0.0800,0.0079,0.9499,0.0017</t>
-  </si>
-  <si>
-    <t>0.0315,0.9574,0.0014,0.0021</t>
-  </si>
-  <si>
-    <t>0.0249,0.9730,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.1314,0.8793,0.0075,0.0051</t>
-  </si>
-  <si>
-    <t>0.2815,0.6666,0.1436,0.0129</t>
-  </si>
-  <si>
-    <t>0.1535,0.8679,0.0076,0.0010</t>
-  </si>
-  <si>
-    <t>0.0176,0.9746,0.0040,0.0004</t>
-  </si>
-  <si>
-    <t>0.6659,0.4375,0.0094,0.0033</t>
-  </si>
-  <si>
-    <t>0.2191,0.4363,0.4097,0.0202</t>
-  </si>
-  <si>
-    <t>0.2352,0.0493,0.7485,0.0265</t>
-  </si>
-  <si>
-    <t>0.4654,0.2844,0.0945,0.0657</t>
-  </si>
-  <si>
-    <t>0.2978,0.0553,0.7100,0.0081</t>
-  </si>
-  <si>
-    <t>0.1555,0.0192,0.1036,0.8095</t>
-  </si>
-  <si>
-    <t>0.0157,0.9566,0.0813,0.0010</t>
-  </si>
-  <si>
-    <t>0.0020,0.9785,0.0242,0.0086</t>
-  </si>
-  <si>
-    <t>0.0309,0.8609,0.1141,0.0814</t>
-  </si>
-  <si>
-    <t>0.0055,0.9136,0.7657,0.0012</t>
-  </si>
-  <si>
-    <t>0.0059,0.9799,0.1001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8503,0.1229,0.0386,0.0017</t>
-  </si>
-  <si>
-    <t>0.4298,0.6271,0.0275,0.0025</t>
-  </si>
-  <si>
-    <t>0.9774,0.0081,0.0072,0.0016</t>
-  </si>
-  <si>
-    <t>0.9854,0.0030,0.0017,0.0030</t>
-  </si>
-  <si>
-    <t>0.9783,0.0030,0.0017,0.0112</t>
-  </si>
-  <si>
-    <t>0.9295,0.0316,0.0342,0.0041</t>
-  </si>
-  <si>
-    <t>0.9915,0.0013,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9503,0.0147,0.0259,0.0053</t>
-  </si>
-  <si>
-    <t>0.9684,0.0129,0.0075,0.0048</t>
-  </si>
-  <si>
-    <t>0.9767,0.0048,0.0023,0.0082</t>
-  </si>
-  <si>
-    <t>0.0030,0.5734,0.9621,0.0006</t>
-  </si>
-  <si>
-    <t>0.0468,0.3178,0.7828,0.0032</t>
-  </si>
-  <si>
-    <t>0.0606,0.3776,0.6553,0.0105</t>
-  </si>
-  <si>
-    <t>0.0196,0.0918,0.9415,0.0005</t>
-  </si>
-  <si>
-    <t>0.6187,0.0250,0.3815,0.0380</t>
-  </si>
-  <si>
-    <t>0.3826,0.0442,0.6203,0.0144</t>
-  </si>
-  <si>
-    <t>0.3173,0.0096,0.8443,0.0024</t>
-  </si>
-  <si>
-    <t>0.6147,0.2031,0.2213,0.0139</t>
-  </si>
-  <si>
-    <t>0.0273,0.0048,0.0021,0.9880</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.0021,0.9984</t>
-  </si>
-  <si>
-    <t>0.0135,0.0006,0.0007,0.9936</t>
-  </si>
-  <si>
-    <t>0.0266,0.0011,0.0052,0.9821</t>
-  </si>
-  <si>
-    <t>0.0025,0.9079,0.7974,0.0017</t>
-  </si>
-  <si>
-    <t>0.9388,0.0573,0.0091,0.0047</t>
-  </si>
-  <si>
-    <t>0.4904,0.5766,0.0231,0.0073</t>
-  </si>
-  <si>
-    <t>0.9836,0.0072,0.0015,0.0025</t>
-  </si>
-  <si>
-    <t>0.6078,0.4311,0.0304,0.0023</t>
-  </si>
-  <si>
-    <t>0.8949,0.0124,0.0156,0.0566</t>
-  </si>
-  <si>
-    <t>0.2683,0.0022,0.0149,0.8141</t>
-  </si>
-  <si>
-    <t>0.8909,0.0372,0.0748,0.0050</t>
-  </si>
-  <si>
-    <t>0.0039,0.0497,0.9809,0.0103</t>
-  </si>
-  <si>
-    <t>0.2894,0.0012,0.0149,0.8003</t>
-  </si>
-  <si>
-    <t>0.8409,0.0738,0.0389,0.0234</t>
-  </si>
-  <si>
-    <t>0.4740,0.5272,0.0363,0.0065</t>
-  </si>
-  <si>
-    <t>0.9232,0.0190,0.0520,0.0019</t>
-  </si>
-  <si>
-    <t>0.8662,0.0630,0.0639,0.0037</t>
-  </si>
-  <si>
-    <t>0.4472,0.3799,0.2004,0.0232</t>
-  </si>
-  <si>
-    <t>0.7805,0.0998,0.1537,0.0105</t>
-  </si>
-  <si>
-    <t>0.6211,0.4066,0.0374,0.0063</t>
-  </si>
-  <si>
-    <t>0.9689,0.0271,0.0009,0.0031</t>
-  </si>
-  <si>
-    <t>0.9921,0.0021,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9921,0.0010,0.0006,0.0022</t>
-  </si>
-  <si>
-    <t>0.9883,0.0021,0.0011,0.0026</t>
-  </si>
-  <si>
-    <t>0.9868,0.0043,0.0016,0.0025</t>
-  </si>
-  <si>
-    <t>0.9549,0.0225,0.0063,0.0071</t>
-  </si>
-  <si>
-    <t>0.9860,0.0040,0.0031,0.0019</t>
-  </si>
-  <si>
-    <t>0.9905,0.0046,0.0016,0.0008</t>
-  </si>
-  <si>
-    <t>0.5076,0.5303,0.0067,0.0060</t>
-  </si>
-  <si>
-    <t>0.8431,0.1606,0.0209,0.0055</t>
-  </si>
-  <si>
-    <t>0.7704,0.3788,0.0021,0.0012</t>
-  </si>
-  <si>
-    <t>0.3937,0.5500,0.2053,0.0227</t>
-  </si>
-  <si>
-    <t>0.9471,0.0451,0.0088,0.0028</t>
-  </si>
-  <si>
-    <t>0.7635,0.1650,0.0631,0.0323</t>
-  </si>
-  <si>
-    <t>0.9308,0.0641,0.0114,0.0032</t>
-  </si>
-  <si>
-    <t>0.9276,0.0606,0.0137,0.0031</t>
-  </si>
-  <si>
-    <t>0.0009,0.1257,0.9918,0.0014</t>
-  </si>
-  <si>
-    <t>0.9495,0.0460,0.0104,0.0013</t>
-  </si>
-  <si>
-    <t>0.0085,0.0058,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0591,0.0560,0.9341,0.0006</t>
-  </si>
-  <si>
-    <t>0.0033,0.0049,0.9932,0.0029</t>
-  </si>
-  <si>
-    <t>0.0151,0.0616,0.9743,0.0005</t>
-  </si>
-  <si>
-    <t>0.0040,0.0863,0.9838,0.0007</t>
-  </si>
-  <si>
-    <t>0.0022,0.0012,0.9950,0.0022</t>
-  </si>
-  <si>
-    <t>0.0110,0.0184,0.9833,0.0004</t>
-  </si>
-  <si>
-    <t>0.6225,0.0349,0.3512,0.0369</t>
-  </si>
-  <si>
-    <t>0.4532,0.0408,0.5615,0.0034</t>
-  </si>
-  <si>
-    <t>0.7230,0.0526,0.2741,0.0053</t>
-  </si>
-  <si>
-    <t>0.3992,0.1752,0.4049,0.0032</t>
-  </si>
-  <si>
-    <t>0.3736,0.0787,0.5967,0.0046</t>
-  </si>
-  <si>
-    <t>0.7484,0.0109,0.3666,0.0037</t>
-  </si>
-  <si>
-    <t>0.6991,0.0768,0.2180,0.0170</t>
-  </si>
-  <si>
-    <t>0.2575,0.0420,0.7699,0.0369</t>
-  </si>
-  <si>
-    <t>0.7967,0.2223,0.0130,0.0075</t>
-  </si>
-  <si>
-    <t>0.6389,0.4357,0.0163,0.0057</t>
-  </si>
-  <si>
-    <t>0.8544,0.1285,0.0377,0.0087</t>
-  </si>
-  <si>
-    <t>0.8790,0.0960,0.0432,0.0047</t>
-  </si>
-  <si>
-    <t>0.6249,0.4401,0.0218,0.0070</t>
-  </si>
-  <si>
-    <t>0.4958,0.1867,0.3725,0.0146</t>
-  </si>
-  <si>
-    <t>0.6350,0.0173,0.4004,0.0236</t>
-  </si>
-  <si>
-    <t>0.3262,0.4007,0.3176,0.1313</t>
-  </si>
-  <si>
-    <t>0.6085,0.0232,0.5267,0.0023</t>
-  </si>
-  <si>
-    <t>0.7532,0.0082,0.1080,0.0770</t>
-  </si>
-  <si>
-    <t>0.0199,0.0101,0.9551,0.0307</t>
-  </si>
-  <si>
-    <t>0.0160,0.4588,0.6656,0.0704</t>
-  </si>
-  <si>
-    <t>0.0281,0.0753,0.8737,0.0921</t>
-  </si>
-  <si>
-    <t>0.1302,0.0598,0.8509,0.0247</t>
-  </si>
-  <si>
-    <t>0.0220,0.1211,0.9221,0.0142</t>
-  </si>
-  <si>
-    <t>0.9756,0.0148,0.0030,0.0028</t>
-  </si>
-  <si>
-    <t>0.9662,0.0227,0.0049,0.0039</t>
-  </si>
-  <si>
-    <t>0.9523,0.0312,0.0059,0.0051</t>
-  </si>
-  <si>
-    <t>0.9488,0.0717,0.0030,0.0015</t>
-  </si>
-  <si>
-    <t>0.9773,0.0155,0.0021,0.0023</t>
-  </si>
-  <si>
-    <t>0.9667,0.0340,0.0039,0.0016</t>
-  </si>
-  <si>
-    <t>0.9888,0.0027,0.0009,0.0035</t>
-  </si>
-  <si>
-    <t>0.9666,0.0142,0.0037,0.0059</t>
-  </si>
-  <si>
-    <t>0.1777,0.0436,0.8673,0.0039</t>
-  </si>
-  <si>
-    <t>0.0815,0.6314,0.4989,0.0129</t>
-  </si>
-  <si>
-    <t>0.8473,0.0264,0.0926,0.0293</t>
-  </si>
-  <si>
-    <t>0.0067,0.0182,0.9854,0.0025</t>
-  </si>
-  <si>
-    <t>0.0016,0.0167,0.9779,0.0224</t>
-  </si>
-  <si>
-    <t>0.0293,0.1028,0.9044,0.0026</t>
-  </si>
-  <si>
-    <t>0.0022,0.0070,0.9938,0.0034</t>
-  </si>
-  <si>
-    <t>0.0605,0.0427,0.9032,0.0064</t>
-  </si>
-  <si>
-    <t>0.0051,0.0029,0.9839,0.0117</t>
-  </si>
-  <si>
-    <t>0.0097,0.0096,0.9817,0.0046</t>
-  </si>
-  <si>
-    <t>0.0478,0.1144,0.8850,0.0107</t>
-  </si>
-  <si>
-    <t>0.6209,0.0315,0.3826,0.0335</t>
-  </si>
-  <si>
-    <t>0.6348,0.0093,0.1871,0.1554</t>
-  </si>
-  <si>
-    <t>0.8559,0.0102,0.1703,0.0022</t>
-  </si>
-  <si>
-    <t>0.9742,0.0088,0.0024,0.0040</t>
-  </si>
-  <si>
-    <t>0.9905,0.0062,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9879,0.0084,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9899,0.0036,0.0015,0.0011</t>
-  </si>
-  <si>
-    <t>0.9542,0.0248,0.0135,0.0062</t>
-  </si>
-  <si>
-    <t>0.9542,0.0413,0.0092,0.0015</t>
-  </si>
-  <si>
-    <t>0.9796,0.0050,0.0007,0.0065</t>
-  </si>
-  <si>
-    <t>0.9782,0.0133,0.0026,0.0025</t>
-  </si>
-  <si>
-    <t>0.1416,0.1764,0.6345,0.0559</t>
-  </si>
-  <si>
-    <t>0.0065,0.0405,0.9816,0.0025</t>
-  </si>
-  <si>
-    <t>0.0159,0.0886,0.9363,0.0057</t>
-  </si>
-  <si>
-    <t>0.0595,0.0222,0.8923,0.0231</t>
-  </si>
-  <si>
-    <t>0.0077,0.0010,0.9897,0.0019</t>
-  </si>
-  <si>
-    <t>0.1380,0.0055,0.8214,0.0806</t>
-  </si>
-  <si>
-    <t>0.0997,0.0239,0.8792,0.0198</t>
-  </si>
-  <si>
-    <t>0.0366,0.0331,0.7694,0.2060</t>
-  </si>
-  <si>
-    <t>0.7181,0.0010,0.0089,0.3174</t>
-  </si>
-  <si>
-    <t>0.0253,0.0269,0.0050,0.9835</t>
-  </si>
-  <si>
-    <t>0.0311,0.0035,0.0008,0.9895</t>
-  </si>
-  <si>
-    <t>0.0028,0.0003,0.0002,0.9987</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.0009,0.9970</t>
-  </si>
-  <si>
-    <t>0.5107,0.0133,0.0131,0.5856</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.3385,0.0427,0.0349,0.7138</t>
+  </si>
+  <si>
+    <t>0.0026,0.0015,0.0015,0.9975</t>
+  </si>
+  <si>
+    <t>0.7078,0.0107,0.0023,0.3217</t>
+  </si>
+  <si>
+    <t>0.0067,0.0112,0.0007,0.9963</t>
+  </si>
+  <si>
+    <t>0.9949,0.0026,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0006,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9913,0.0035,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9893,0.0037,0.0021,0.0013</t>
+  </si>
+  <si>
+    <t>0.9865,0.0069,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9725,0.0257,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.9882,0.0025,0.0008,0.0036</t>
+  </si>
+  <si>
+    <t>0.9823,0.0053,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.7412,0.0522,0.2079,0.0043</t>
+  </si>
+  <si>
+    <t>0.2996,0.0359,0.7849,0.0053</t>
+  </si>
+  <si>
+    <t>0.1936,0.0257,0.8562,0.0088</t>
+  </si>
+  <si>
+    <t>0.0320,0.0247,0.9660,0.0013</t>
+  </si>
+  <si>
+    <t>0.7747,0.1021,0.0995,0.0197</t>
+  </si>
+  <si>
+    <t>0.0170,0.9649,0.0436,0.0010</t>
+  </si>
+  <si>
+    <t>0.0049,0.9881,0.0075,0.0006</t>
+  </si>
+  <si>
+    <t>0.0952,0.8957,0.0052,0.0022</t>
+  </si>
+  <si>
+    <t>0.0274,0.9586,0.0096,0.0034</t>
+  </si>
+  <si>
+    <t>0.0089,0.9860,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.1152,0.0279,0.8456,0.0402</t>
+  </si>
+  <si>
+    <t>0.7397,0.0115,0.2635,0.0149</t>
+  </si>
+  <si>
+    <t>0.0157,0.0042,0.9739,0.0120</t>
+  </si>
+  <si>
+    <t>0.2538,0.0180,0.8184,0.0063</t>
+  </si>
+  <si>
+    <t>0.0911,0.0095,0.8884,0.0252</t>
+  </si>
+  <si>
+    <t>0.0711,0.0077,0.9460,0.0062</t>
+  </si>
+  <si>
+    <t>0.0032,0.0026,0.9913,0.0051</t>
+  </si>
+  <si>
+    <t>0.7403,0.3632,0.0077,0.0012</t>
+  </si>
+  <si>
+    <t>0.4143,0.2163,0.4449,0.0094</t>
+  </si>
+  <si>
+    <t>0.0017,0.0099,0.9927,0.0049</t>
+  </si>
+  <si>
+    <t>0.0116,0.9474,0.1424,0.0012</t>
+  </si>
+  <si>
+    <t>0.5792,0.1897,0.2178,0.0735</t>
+  </si>
+  <si>
+    <t>0.7873,0.1281,0.0895,0.0240</t>
+  </si>
+  <si>
+    <t>0.7728,0.2873,0.0122,0.0043</t>
+  </si>
+  <si>
+    <t>0.0611,0.9118,0.1044,0.0036</t>
+  </si>
+  <si>
+    <t>0.0025,0.9290,0.3521,0.0062</t>
+  </si>
+  <si>
+    <t>0.0210,0.0701,0.8757,0.0757</t>
+  </si>
+  <si>
+    <t>0.0943,0.1366,0.8004,0.0597</t>
+  </si>
+  <si>
+    <t>0.0295,0.0233,0.8866,0.1228</t>
+  </si>
+  <si>
+    <t>0.0372,0.1042,0.9117,0.0203</t>
+  </si>
+  <si>
+    <t>0.0240,0.8923,0.1148,0.0184</t>
+  </si>
+  <si>
+    <t>0.0323,0.0176,0.9515,0.0100</t>
+  </si>
+  <si>
+    <t>0.0323,0.8010,0.0086,0.8704</t>
+  </si>
+  <si>
+    <t>0.0121,0.9568,0.0207,0.0162</t>
+  </si>
+  <si>
+    <t>0.0006,0.9930,0.0349,0.0007</t>
+  </si>
+  <si>
+    <t>0.0090,0.9555,0.0846,0.0054</t>
+  </si>
+  <si>
+    <t>0.0754,0.3109,0.7433,0.0290</t>
+  </si>
+  <si>
+    <t>0.0092,0.3387,0.9530,0.0053</t>
+  </si>
+  <si>
+    <t>0.0138,0.0218,0.9666,0.0132</t>
+  </si>
+  <si>
+    <t>0.0238,0.0041,0.9806,0.0016</t>
+  </si>
+  <si>
+    <t>0.0023,0.0121,0.9886,0.0057</t>
+  </si>
+  <si>
+    <t>0.0448,0.3680,0.8394,0.0023</t>
+  </si>
+  <si>
+    <t>0.9168,0.1003,0.0069,0.0023</t>
+  </si>
+  <si>
+    <t>0.9653,0.0131,0.0164,0.0032</t>
+  </si>
+  <si>
+    <t>0.9282,0.0633,0.0145,0.0112</t>
+  </si>
+  <si>
+    <t>0.0190,0.0623,0.9750,0.0078</t>
+  </si>
+  <si>
+    <t>0.9419,0.0495,0.0098,0.0027</t>
+  </si>
+  <si>
+    <t>0.9825,0.0127,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9740,0.0123,0.0046,0.0028</t>
+  </si>
+  <si>
+    <t>0.0027,0.8962,0.7553,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.1611,0.9823,0.0013</t>
+  </si>
+  <si>
+    <t>0.0039,0.2608,0.7359,0.0535</t>
+  </si>
+  <si>
+    <t>0.0033,0.6203,0.9604,0.0010</t>
+  </si>
+  <si>
+    <t>0.0244,0.0277,0.9670,0.0035</t>
+  </si>
+  <si>
+    <t>0.0277,0.8910,0.1732,0.0015</t>
+  </si>
+  <si>
+    <t>0.0108,0.9809,0.0086,0.0002</t>
+  </si>
+  <si>
+    <t>0.8917,0.0426,0.0429,0.0107</t>
+  </si>
+  <si>
+    <t>0.7121,0.0245,0.4719,0.0032</t>
+  </si>
+  <si>
+    <t>0.4754,0.1408,0.3296,0.0032</t>
+  </si>
+  <si>
+    <t>0.0005,0.9472,0.9139,0.0000</t>
+  </si>
+  <si>
+    <t>0.0396,0.5956,0.6910,0.0024</t>
+  </si>
+  <si>
+    <t>0.0005,0.9921,0.1799,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9622,0.8847,0.0001</t>
+  </si>
+  <si>
+    <t>0.0252,0.0077,0.0262,0.9691</t>
+  </si>
+  <si>
+    <t>0.0009,0.0053,0.0004,0.9991</t>
+  </si>
+  <si>
+    <t>0.0077,0.0029,0.0015,0.9948</t>
+  </si>
+  <si>
+    <t>0.0161,0.0019,0.0003,0.9951</t>
+  </si>
+  <si>
+    <t>0.0380,0.0221,0.0154,0.9679</t>
+  </si>
+  <si>
+    <t>0.0121,0.0056,0.0025,0.9923</t>
+  </si>
+  <si>
+    <t>0.0045,0.9335,0.6094,0.0004</t>
+  </si>
+  <si>
+    <t>0.0048,0.7256,0.9297,0.0007</t>
+  </si>
+  <si>
+    <t>0.0065,0.8892,0.6026,0.0008</t>
+  </si>
+  <si>
+    <t>0.0109,0.7739,0.8173,0.0029</t>
+  </si>
+  <si>
+    <t>0.0013,0.9172,0.8944,0.0001</t>
+  </si>
+  <si>
+    <t>0.0082,0.7218,0.8984,0.0029</t>
+  </si>
+  <si>
+    <t>0.9888,0.0060,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9591,0.0587,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9865,0.0029,0.0004,0.0034</t>
+  </si>
+  <si>
+    <t>0.9847,0.0103,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9722,0.0177,0.0018,0.0031</t>
+  </si>
+  <si>
+    <t>0.9820,0.0077,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9721,0.0258,0.0043,0.0014</t>
+  </si>
+  <si>
+    <t>0.9905,0.0033,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9944,0.0009,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9932,0.0026,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9926,0.0003,0.0000,0.0042</t>
+  </si>
+  <si>
+    <t>0.9917,0.0021,0.0011,0.0015</t>
+  </si>
+  <si>
+    <t>0.9945,0.0010,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0062,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9824,0.0086,0.0022,0.0023</t>
+  </si>
+  <si>
+    <t>0.9928,0.0022,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0073,0.0032,0.9854,0.0064</t>
+  </si>
+  <si>
+    <t>0.0284,0.0602,0.9499,0.0012</t>
+  </si>
+  <si>
+    <t>0.5389,0.0029,0.1922,0.1750</t>
+  </si>
+  <si>
+    <t>0.0719,0.0037,0.9562,0.0027</t>
+  </si>
+  <si>
+    <t>0.0223,0.9670,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.0621,0.9357,0.0087,0.0003</t>
+  </si>
+  <si>
+    <t>0.0129,0.9744,0.0050,0.0016</t>
+  </si>
+  <si>
+    <t>0.0542,0.9329,0.0065,0.0048</t>
+  </si>
+  <si>
+    <t>0.0404,0.9532,0.0018,0.0040</t>
+  </si>
+  <si>
+    <t>0.0125,0.9781,0.0019,0.0015</t>
+  </si>
+  <si>
+    <t>0.5338,0.4673,0.0174,0.0333</t>
+  </si>
+  <si>
+    <t>0.6922,0.0129,0.3942,0.0081</t>
+  </si>
+  <si>
+    <t>0.0390,0.0162,0.9363,0.0265</t>
+  </si>
+  <si>
+    <t>0.4364,0.1204,0.4169,0.0043</t>
+  </si>
+  <si>
+    <t>0.6599,0.0768,0.3071,0.0171</t>
+  </si>
+  <si>
+    <t>0.1093,0.0992,0.0639,0.8763</t>
+  </si>
+  <si>
+    <t>0.0032,0.9858,0.0257,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.9852,0.0215,0.0051</t>
+  </si>
+  <si>
+    <t>0.0035,0.9534,0.0081,0.4266</t>
+  </si>
+  <si>
+    <t>0.0041,0.9678,0.2119,0.0013</t>
+  </si>
+  <si>
+    <t>0.0339,0.9410,0.0819,0.0006</t>
+  </si>
+  <si>
+    <t>0.6897,0.4276,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.3863,0.6705,0.0333,0.0024</t>
+  </si>
+  <si>
+    <t>0.9835,0.0051,0.0056,0.0012</t>
+  </si>
+  <si>
+    <t>0.9731,0.0099,0.0077,0.0036</t>
+  </si>
+  <si>
+    <t>0.9508,0.0111,0.0195,0.0077</t>
+  </si>
+  <si>
+    <t>0.9653,0.0084,0.0060,0.0058</t>
+  </si>
+  <si>
+    <t>0.9905,0.0028,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.9194,0.0249,0.0703,0.0039</t>
+  </si>
+  <si>
+    <t>0.9749,0.0084,0.0065,0.0036</t>
+  </si>
+  <si>
+    <t>0.9694,0.0199,0.0059,0.0016</t>
+  </si>
+  <si>
+    <t>0.0066,0.8187,0.6912,0.0014</t>
+  </si>
+  <si>
+    <t>0.0217,0.5090,0.8863,0.0020</t>
+  </si>
+  <si>
+    <t>0.0597,0.1026,0.8795,0.0254</t>
+  </si>
+  <si>
+    <t>0.1209,0.1540,0.7248,0.0027</t>
+  </si>
+  <si>
+    <t>0.8252,0.0887,0.0573,0.0199</t>
+  </si>
+  <si>
+    <t>0.7426,0.0368,0.2011,0.0027</t>
+  </si>
+  <si>
+    <t>0.4086,0.0049,0.5509,0.0899</t>
+  </si>
+  <si>
+    <t>0.7889,0.0220,0.2041,0.0091</t>
+  </si>
+  <si>
+    <t>0.0125,0.0028,0.0023,0.9924</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.0026,0.9984</t>
+  </si>
+  <si>
+    <t>0.0059,0.0470,0.0038,0.9926</t>
+  </si>
+  <si>
+    <t>0.0150,0.0047,0.0029,0.9909</t>
+  </si>
+  <si>
+    <t>0.0019,0.8838,0.5008,0.0044</t>
+  </si>
+  <si>
+    <t>0.9299,0.0786,0.0071,0.0018</t>
+  </si>
+  <si>
+    <t>0.6016,0.5254,0.0062,0.0051</t>
+  </si>
+  <si>
+    <t>0.9770,0.0036,0.0020,0.0087</t>
+  </si>
+  <si>
+    <t>0.5525,0.4886,0.0317,0.0048</t>
+  </si>
+  <si>
+    <t>0.9502,0.0109,0.0132,0.0126</t>
+  </si>
+  <si>
+    <t>0.2901,0.0043,0.0097,0.8506</t>
+  </si>
+  <si>
+    <t>0.9430,0.0051,0.0092,0.0255</t>
+  </si>
+  <si>
+    <t>0.0134,0.1656,0.7485,0.1936</t>
+  </si>
+  <si>
+    <t>0.7197,0.0015,0.0075,0.3695</t>
+  </si>
+  <si>
+    <t>0.9336,0.0053,0.0070,0.0337</t>
+  </si>
+  <si>
+    <t>0.3182,0.6008,0.1453,0.0231</t>
+  </si>
+  <si>
+    <t>0.9628,0.0216,0.0044,0.0016</t>
+  </si>
+  <si>
+    <t>0.9085,0.0471,0.0302,0.0040</t>
+  </si>
+  <si>
+    <t>0.2860,0.6304,0.0970,0.0060</t>
+  </si>
+  <si>
+    <t>0.5215,0.4070,0.0889,0.0037</t>
+  </si>
+  <si>
+    <t>0.8822,0.0858,0.0178,0.0076</t>
+  </si>
+  <si>
+    <t>0.9853,0.0043,0.0017,0.0025</t>
+  </si>
+  <si>
+    <t>0.9886,0.0020,0.0005,0.0037</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9826,0.0038,0.0017,0.0036</t>
+  </si>
+  <si>
+    <t>0.8983,0.0743,0.0370,0.0026</t>
+  </si>
+  <si>
+    <t>0.9622,0.0238,0.0043,0.0061</t>
+  </si>
+  <si>
+    <t>0.9930,0.0020,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9817,0.0055,0.0047,0.0018</t>
+  </si>
+  <si>
+    <t>0.5383,0.4825,0.0043,0.0059</t>
+  </si>
+  <si>
+    <t>0.6572,0.5064,0.0049,0.0011</t>
+  </si>
+  <si>
+    <t>0.4807,0.6000,0.0175,0.0015</t>
+  </si>
+  <si>
+    <t>0.2315,0.7058,0.1063,0.0192</t>
+  </si>
+  <si>
+    <t>0.9266,0.1197,0.0016,0.0016</t>
+  </si>
+  <si>
+    <t>0.8925,0.0570,0.0524,0.0070</t>
+  </si>
+  <si>
+    <t>0.9860,0.0098,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.9416,0.0341,0.0147,0.0053</t>
+  </si>
+  <si>
+    <t>0.0035,0.0463,0.9926,0.0019</t>
+  </si>
+  <si>
+    <t>0.9591,0.0173,0.0084,0.0066</t>
+  </si>
+  <si>
+    <t>0.0061,0.0033,0.9938,0.0007</t>
+  </si>
+  <si>
+    <t>0.0096,0.1081,0.9616,0.0058</t>
+  </si>
+  <si>
+    <t>0.0296,0.0099,0.9699,0.0011</t>
+  </si>
+  <si>
+    <t>0.0218,0.4350,0.8667,0.0031</t>
+  </si>
+  <si>
+    <t>0.0766,0.0152,0.9542,0.0008</t>
+  </si>
+  <si>
+    <t>0.0064,0.0037,0.9912,0.0015</t>
+  </si>
+  <si>
+    <t>0.0028,0.0660,0.9882,0.0008</t>
+  </si>
+  <si>
+    <t>0.2907,0.0659,0.6985,0.0180</t>
+  </si>
+  <si>
+    <t>0.0539,0.1211,0.9196,0.0023</t>
+  </si>
+  <si>
+    <t>0.1326,0.0270,0.8397,0.0250</t>
+  </si>
+  <si>
+    <t>0.2116,0.4224,0.2839,0.0028</t>
+  </si>
+  <si>
+    <t>0.4571,0.1512,0.3251,0.0018</t>
+  </si>
+  <si>
+    <t>0.5390,0.3060,0.1187,0.0040</t>
+  </si>
+  <si>
+    <t>0.7237,0.0586,0.0868,0.0478</t>
+  </si>
+  <si>
+    <t>0.2737,0.1333,0.5675,0.0514</t>
+  </si>
+  <si>
+    <t>0.6293,0.4530,0.0119,0.0050</t>
+  </si>
+  <si>
+    <t>0.2859,0.7570,0.0070,0.0044</t>
+  </si>
+  <si>
+    <t>0.8356,0.2065,0.0132,0.0042</t>
+  </si>
+  <si>
+    <t>0.9580,0.0326,0.0046,0.0032</t>
+  </si>
+  <si>
+    <t>0.8084,0.2633,0.0108,0.0018</t>
+  </si>
+  <si>
+    <t>0.4449,0.1610,0.4000,0.0112</t>
+  </si>
+  <si>
+    <t>0.7938,0.0301,0.1855,0.0328</t>
+  </si>
+  <si>
+    <t>0.7828,0.0242,0.1685,0.0095</t>
+  </si>
+  <si>
+    <t>0.7496,0.0153,0.1270,0.1085</t>
+  </si>
+  <si>
+    <t>0.5512,0.0212,0.1668,0.2237</t>
+  </si>
+  <si>
+    <t>0.0440,0.0207,0.9338,0.0266</t>
+  </si>
+  <si>
+    <t>0.1093,0.3638,0.5949,0.0192</t>
+  </si>
+  <si>
+    <t>0.0239,0.2985,0.9190,0.0044</t>
+  </si>
+  <si>
+    <t>0.0245,0.0187,0.9734,0.0034</t>
+  </si>
+  <si>
+    <t>0.0183,0.5529,0.6935,0.0099</t>
+  </si>
+  <si>
+    <t>0.9786,0.0072,0.0028,0.0037</t>
+  </si>
+  <si>
+    <t>0.9933,0.0029,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9774,0.0074,0.0019,0.0051</t>
+  </si>
+  <si>
+    <t>0.9663,0.0307,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.9786,0.0159,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9807,0.0069,0.0036,0.0022</t>
+  </si>
+  <si>
+    <t>0.9954,0.0004,0.0000,0.0017</t>
+  </si>
+  <si>
+    <t>0.9933,0.0016,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.0277,0.0078,0.9753,0.0032</t>
+  </si>
+  <si>
+    <t>0.4672,0.1227,0.4513,0.0734</t>
+  </si>
+  <si>
+    <t>0.9149,0.0298,0.0206,0.0193</t>
+  </si>
+  <si>
+    <t>0.0050,0.0100,0.9887,0.0040</t>
+  </si>
+  <si>
+    <t>0.0022,0.0335,0.9915,0.0018</t>
+  </si>
+  <si>
+    <t>0.0507,0.1010,0.8888,0.0085</t>
+  </si>
+  <si>
+    <t>0.0003,0.0015,0.9986,0.0007</t>
+  </si>
+  <si>
+    <t>0.0868,0.0422,0.8997,0.0016</t>
+  </si>
+  <si>
+    <t>0.0143,0.0171,0.9812,0.0030</t>
+  </si>
+  <si>
+    <t>0.0075,0.0272,0.9663,0.0072</t>
+  </si>
+  <si>
+    <t>0.0322,0.2094,0.8328,0.0404</t>
+  </si>
+  <si>
+    <t>0.8448,0.0032,0.2334,0.0027</t>
+  </si>
+  <si>
+    <t>0.7213,0.0075,0.3678,0.0138</t>
+  </si>
+  <si>
+    <t>0.8304,0.0110,0.1410,0.0123</t>
+  </si>
+  <si>
+    <t>0.9799,0.0141,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9762,0.0177,0.0043,0.0009</t>
+  </si>
+  <si>
+    <t>0.9889,0.0067,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9802,0.0090,0.0023,0.0028</t>
+  </si>
+  <si>
+    <t>0.9920,0.0027,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9701,0.0364,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9842,0.0077,0.0015,0.0016</t>
+  </si>
+  <si>
+    <t>0.9917,0.0032,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.0381,0.0691,0.9233,0.0037</t>
+  </si>
+  <si>
+    <t>0.0019,0.0343,0.9922,0.0021</t>
+  </si>
+  <si>
+    <t>0.0054,0.0639,0.9825,0.0010</t>
+  </si>
+  <si>
+    <t>0.0729,0.1972,0.7204,0.0041</t>
+  </si>
+  <si>
+    <t>0.0256,0.0067,0.9734,0.0037</t>
+  </si>
+  <si>
+    <t>0.2594,0.0112,0.6866,0.0849</t>
+  </si>
+  <si>
+    <t>0.0955,0.0193,0.8721,0.0478</t>
+  </si>
+  <si>
+    <t>0.0269,0.0231,0.9359,0.0510</t>
+  </si>
+  <si>
+    <t>0.5891,0.0116,0.0037,0.5691</t>
+  </si>
+  <si>
+    <t>0.0080,0.0041,0.0025,0.9942</t>
+  </si>
+  <si>
+    <t>0.0492,0.0075,0.0054,0.9737</t>
+  </si>
+  <si>
+    <t>0.0117,0.0013,0.0020,0.9925</t>
+  </si>
+  <si>
+    <t>0.0059,0.0004,0.0001,0.9982</t>
+  </si>
+  <si>
+    <t>0.1698,0.0182,0.0203,0.8926</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
